--- a/Configs/GameConfig/Datas/fg/#Producer-生产参数.xlsx
+++ b/Configs/GameConfig/Datas/fg/#Producer-生产参数.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -946,6 +946,194 @@
         <v>25</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>parts_workshop</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>recipe</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>part,structural,repair_kit</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>prod.place.any</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>electronics_bench</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>recipe</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>electronic,precision_part,chip_substrate</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>prod.place.any</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>component_workshop</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>recipe</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>combat_component,structure_module</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>prod.place.any</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>firmware_burner</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>recipe</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>firmware_chip</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>prod.place.any</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#Producer-生产参数.xlsx
+++ b/Configs/GameConfig/Datas/fg/#Producer-生产参数.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1134,6 +1134,53 @@
         <v>100</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>fuel_generator</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>generator</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>30</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>120</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>prod.place.any</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>70</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#Producer-生产参数.xlsx
+++ b/Configs/GameConfig/Datas/fg/#Producer-生产参数.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1181,6 +1181,53 @@
         <v>70</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>purifier</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>purifier</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>60</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>30</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>prod.place.purifier</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>70</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#Producer-生产参数.xlsx
+++ b/Configs/GameConfig/Datas/fg/#Producer-生产参数.xlsx
@@ -1054,7 +1054,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>combat_component,structure_module</t>
+          <t>combat_component,structure_module,drop_pod</t>
         </is>
       </c>
       <c r="E13" t="n">
